--- a/Result/profitability/3289.xlsx
+++ b/Result/profitability/3289.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>1.26375</v>
+        <v>1.24875</v>
       </c>
       <c r="N2" t="n">
-        <v>27.93</v>
+        <v>27.44625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2825</v>
+        <v>1.25875</v>
       </c>
       <c r="N3" t="n">
-        <v>29.80375</v>
+        <v>29.61875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>1.29875</v>
+        <v>1.215</v>
       </c>
       <c r="N4" t="n">
-        <v>32.20375</v>
+        <v>31.5725</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15625</v>
+        <v>1.0975</v>
       </c>
       <c r="N5" t="n">
-        <v>33.84375</v>
+        <v>33.7275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8775000000000001</v>
+        <v>0.8812500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>34.35875</v>
+        <v>34.56875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6850000000000002</v>
+        <v>0.7237500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>34.79</v>
+        <v>34.85625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6087500000000001</v>
+        <v>0.4812500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>36.11</v>
+        <v>37.2175</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.28</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07749999999999987</v>
+        <v>-0.0774999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>36.0625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1184</v>
+      </c>
+      <c r="D75" t="n">
+        <v>874</v>
+      </c>
+      <c r="E75" t="n">
+        <v>309</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>71</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>69</v>
+      </c>
+      <c r="K75" t="n">
+        <v>89</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.29625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.1625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4975609756097561</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5130283729009844</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3133333333333334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9299999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03436807095343675</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
